--- a/data/50m_Masculino_Absoluto_Braza.xlsx
+++ b/data/50m_Masculino_Absoluto_Braza.xlsx
@@ -772,13 +772,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F9" t="str">
-        <v>00:00:36.35</v>
+        <v>00:00:35.98</v>
       </c>
       <c r="G9">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="H9" s="1">
-        <v>46171.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I9" t="str">
         <v>Deportista</v>
@@ -787,13 +787,13 @@
         <v>50m</v>
       </c>
       <c r="K9" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L9" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M9" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N9" t="str">
         <v>No</v>
@@ -1335,7 +1335,7 @@
         <v>50 Braza</v>
       </c>
       <c r="C22" t="str">
-        <v>DANIEL DIAZ GONZALEZ</v>
+        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
       </c>
       <c r="D22">
         <v>2012</v>
@@ -1344,13 +1344,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F22" t="str">
-        <v>00:00:40.83</v>
+        <v>00:00:40.41</v>
       </c>
       <c r="G22">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="H22" s="1">
-        <v>46081.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I22" t="str">
         <v>Deportista</v>
@@ -1362,10 +1362,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L22" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M22" t="str">
-        <v>CASTELLÓN</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N22" t="str">
         <v>No</v>
@@ -1379,7 +1379,7 @@
         <v>50 Braza</v>
       </c>
       <c r="C23" t="str">
-        <v>ROGER MASCARELL CARRILLO DE ALBORNOZ</v>
+        <v>DANIEL DIAZ GONZALEZ</v>
       </c>
       <c r="D23">
         <v>2012</v>
@@ -1388,13 +1388,13 @@
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F23" t="str">
-        <v>00:00:41.68</v>
+        <v>00:00:40.83</v>
       </c>
       <c r="G23">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="H23" s="1">
-        <v>46171.99949074074</v>
+        <v>46081.99949074074</v>
       </c>
       <c r="I23" t="str">
         <v>Deportista</v>
@@ -1403,13 +1403,13 @@
         <v>50m</v>
       </c>
       <c r="K23" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L23" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
       </c>
       <c r="M23" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLÓN</v>
       </c>
       <c r="N23" t="str">
         <v>No</v>
@@ -1731,22 +1731,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C31" t="str">
-        <v>DAVID SIENRA BUGS</v>
+        <v>VICENTE SILLA TAMARIT</v>
       </c>
       <c r="D31">
-        <v>2004</v>
+        <v>2011</v>
       </c>
       <c r="E31" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F31" t="str">
-        <v>00:01:18.37</v>
+        <v>00:01:18.22</v>
       </c>
       <c r="G31">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="H31" s="1">
-        <v>45255.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I31" t="str">
         <v>Deportista</v>
@@ -1758,10 +1758,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L31" t="str">
-        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M31" t="str">
-        <v>Castellón</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N31" t="str">
         <v>No</v>
@@ -1775,22 +1775,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C32" t="str">
-        <v>VICENTE SILLA TAMARIT</v>
+        <v>DAVID SIENRA BUGS</v>
       </c>
       <c r="D32">
-        <v>2011</v>
+        <v>2004</v>
       </c>
       <c r="E32" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F32" t="str">
-        <v>00:01:18.71</v>
+        <v>00:01:18.37</v>
       </c>
       <c r="G32">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H32" s="1">
-        <v>46173.99949074074</v>
+        <v>45255.99949074074</v>
       </c>
       <c r="I32" t="str">
         <v>Deportista</v>
@@ -1799,13 +1799,13 @@
         <v>50m</v>
       </c>
       <c r="K32" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L32" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>Trofeo Internacional Castalia Castellón - TICC23</v>
       </c>
       <c r="M32" t="str">
-        <v>Vila-Real</v>
+        <v>Castellón</v>
       </c>
       <c r="N32" t="str">
         <v>No</v>
@@ -2039,22 +2039,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C38" t="str">
-        <v>GEORGI ZHELYAZKOV</v>
+        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
       </c>
       <c r="D38">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="E38" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F38" t="str">
-        <v>00:01:24.00</v>
+        <v>00:01:23.65</v>
       </c>
       <c r="G38">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H38" s="1">
-        <v>46173.99949074074</v>
+        <v>46200.99949074074</v>
       </c>
       <c r="I38" t="str">
         <v>Deportista</v>
@@ -2063,13 +2063,13 @@
         <v>50m</v>
       </c>
       <c r="K38" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L38" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M38" t="str">
-        <v>Vila-Real</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N38" t="str">
         <v>No</v>
@@ -2083,22 +2083,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C39" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>GEORGI ZHELYAZKOV</v>
       </c>
       <c r="D39">
-        <v>2002</v>
+        <v>2010</v>
       </c>
       <c r="E39" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F39" t="str">
-        <v>00:01:24.15</v>
+        <v>00:01:24.00</v>
       </c>
       <c r="G39">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H39" s="1">
-        <v>44359.99949074074</v>
+        <v>46173.99949074074</v>
       </c>
       <c r="I39" t="str">
         <v>Deportista</v>
@@ -2107,13 +2107,13 @@
         <v>50m</v>
       </c>
       <c r="K39" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L39" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
       </c>
       <c r="M39" t="str">
-        <v>Sedavi</v>
+        <v>Vila-Real</v>
       </c>
       <c r="N39" t="str">
         <v>No</v>
@@ -2127,22 +2127,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C40" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D40">
-        <v>2008</v>
+        <v>2002</v>
       </c>
       <c r="E40" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F40" t="str">
-        <v>00:01:24.46</v>
+        <v>00:01:24.15</v>
       </c>
       <c r="G40">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H40" s="1">
-        <v>45094.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I40" t="str">
         <v>Deportista</v>
@@ -2154,10 +2154,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L40" t="str">
-        <v>I Trofeo Federación 226ERS piscina 50m</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M40" t="str">
-        <v>Castellón</v>
+        <v>Sedavi</v>
       </c>
       <c r="N40" t="str">
         <v>No</v>
@@ -2171,22 +2171,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C41" t="str">
-        <v>ONOFRE BONDIA VELERT</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D41">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="E41" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F41" t="str">
-        <v>00:01:24.86</v>
+        <v>00:01:24.46</v>
       </c>
       <c r="G41">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="H41" s="1">
-        <v>44709.99949074074</v>
+        <v>45094.99949074074</v>
       </c>
       <c r="I41" t="str">
         <v>Deportista</v>
@@ -2195,13 +2195,13 @@
         <v>50m</v>
       </c>
       <c r="K41" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L41" t="str">
-        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
+        <v>I Trofeo Federación 226ERS piscina 50m</v>
       </c>
       <c r="M41" t="str">
-        <v>Sedavi</v>
+        <v>Castellón</v>
       </c>
       <c r="N41" t="str">
         <v>No</v>
@@ -2215,22 +2215,22 @@
         <v>100 Braza</v>
       </c>
       <c r="C42" t="str">
-        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
+        <v>ONOFRE BONDIA VELERT</v>
       </c>
       <c r="D42">
-        <v>2012</v>
+        <v>2006</v>
       </c>
       <c r="E42" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F42" t="str">
-        <v>00:01:26.40</v>
+        <v>00:01:24.86</v>
       </c>
       <c r="G42">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="H42" s="1">
-        <v>46081.99949074074</v>
+        <v>44709.99949074074</v>
       </c>
       <c r="I42" t="str">
         <v>Deportista</v>
@@ -2239,13 +2239,13 @@
         <v>50m</v>
       </c>
       <c r="K42" t="str">
-        <v>Electrónico</v>
+        <v>Manual</v>
       </c>
       <c r="L42" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>Control Libre Infantil y 7ª Control Junior y Absoluto Valencia</v>
       </c>
       <c r="M42" t="str">
-        <v>CASTELLÓN</v>
+        <v>Sedavi</v>
       </c>
       <c r="N42" t="str">
         <v>No</v>
@@ -2875,22 +2875,22 @@
         <v>200 Braza</v>
       </c>
       <c r="C57" t="str">
-        <v>MARCOS ESCOBEDO IRURETA</v>
+        <v>VICENTE SILLA TAMARIT</v>
       </c>
       <c r="D57">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="E57" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F57" t="str">
-        <v>00:02:58.35</v>
+        <v>00:02:56.36</v>
       </c>
       <c r="G57">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="H57" s="1">
-        <v>45108.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I57" t="str">
         <v>Deportista</v>
@@ -2902,10 +2902,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L57" t="str">
-        <v>Campeonato Autonomico Infantil de Verano</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M57" t="str">
-        <v>ELDA</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N57" t="str">
         <v>No</v>
@@ -2919,22 +2919,22 @@
         <v>200 Braza</v>
       </c>
       <c r="C58" t="str">
-        <v>FRANCISCO MONCHO GRAMAGE</v>
+        <v>MARCOS ESCOBEDO IRURETA</v>
       </c>
       <c r="D58">
-        <v>1988</v>
+        <v>2008</v>
       </c>
       <c r="E58" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F58" t="str">
-        <v>00:03:01.69</v>
+        <v>00:02:58.35</v>
       </c>
       <c r="G58">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="H58" s="1">
-        <v>44359.99949074074</v>
+        <v>45108.99949074074</v>
       </c>
       <c r="I58" t="str">
         <v>Deportista</v>
@@ -2946,10 +2946,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L58" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>Campeonato Autonomico Infantil de Verano</v>
       </c>
       <c r="M58" t="str">
-        <v>Sedavi</v>
+        <v>ELDA</v>
       </c>
       <c r="N58" t="str">
         <v>No</v>
@@ -2963,22 +2963,22 @@
         <v>200 Braza</v>
       </c>
       <c r="C59" t="str">
-        <v>VICENTE SILLA TAMARIT</v>
+        <v>FRANCISCO MONCHO GRAMAGE</v>
       </c>
       <c r="D59">
-        <v>2011</v>
+        <v>1988</v>
       </c>
       <c r="E59" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F59" t="str">
-        <v>00:03:01.84</v>
+        <v>00:03:01.69</v>
       </c>
       <c r="G59">
         <v>329</v>
       </c>
       <c r="H59" s="1">
-        <v>46172.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I59" t="str">
         <v>Deportista</v>
@@ -2987,13 +2987,13 @@
         <v>50m</v>
       </c>
       <c r="K59" t="str">
-        <v>Manual</v>
+        <v>Electrónico</v>
       </c>
       <c r="L59" t="str">
-        <v>LVI TROFEU SANT PASCUAL XXXVII MEMORIAL JOSE VICENTE MARTI BARRACHINA</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M59" t="str">
-        <v>Vila-Real</v>
+        <v>Sedavi</v>
       </c>
       <c r="N59" t="str">
         <v>No</v>
@@ -3007,22 +3007,22 @@
         <v>200 Braza</v>
       </c>
       <c r="C60" t="str">
-        <v>RAUL VILA ALMAZORA</v>
+        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
       </c>
       <c r="D60">
-        <v>2002</v>
+        <v>2012</v>
       </c>
       <c r="E60" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F60" t="str">
-        <v>00:03:08.00</v>
+        <v>00:03:02.33</v>
       </c>
       <c r="G60">
-        <v>297</v>
+        <v>326</v>
       </c>
       <c r="H60" s="1">
-        <v>44359.99949074074</v>
+        <v>46201.99949074074</v>
       </c>
       <c r="I60" t="str">
         <v>Deportista</v>
@@ -3034,10 +3034,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L60" t="str">
-        <v>IX Trofeo Real Club Natación Delfín</v>
+        <v>CAMPEONATO AUTONOMICO INFANTIL DE VERANO DE LA C.V. 2026</v>
       </c>
       <c r="M60" t="str">
-        <v>Sedavi</v>
+        <v>CASTELLON</v>
       </c>
       <c r="N60" t="str">
         <v>No</v>
@@ -3051,22 +3051,22 @@
         <v>200 Braza</v>
       </c>
       <c r="C61" t="str">
-        <v>FELIPE SEBASTIAN HERMIDA BATTISTON</v>
+        <v>RAUL VILA ALMAZORA</v>
       </c>
       <c r="D61">
-        <v>2012</v>
+        <v>2002</v>
       </c>
       <c r="E61" t="str">
         <v>C.N. MEDITERRANEO VALENCIA</v>
       </c>
       <c r="F61" t="str">
-        <v>00:03:08.23</v>
+        <v>00:03:08.00</v>
       </c>
       <c r="G61">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H61" s="1">
-        <v>46082.99949074074</v>
+        <v>44359.99949074074</v>
       </c>
       <c r="I61" t="str">
         <v>Deportista</v>
@@ -3078,10 +3078,10 @@
         <v>Electrónico</v>
       </c>
       <c r="L61" t="str">
-        <v>CAMPEONATO AUTONOMICO INFANTIL DE INVIERNO 2026</v>
+        <v>IX Trofeo Real Club Natación Delfín</v>
       </c>
       <c r="M61" t="str">
-        <v>CASTELLÓN</v>
+        <v>Sedavi</v>
       </c>
       <c r="N61" t="str">
         <v>No</v>
